--- a/sc_court_records.xlsx
+++ b/sc_court_records.xlsx
@@ -413,10 +413,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -466,6 +466,182 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cherokee</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Brewton, Faith Trammell</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026CP1100431</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dorchester</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Drb Capital Llc</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026CP1801140</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Dorchester</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J G Wentworth Originations Llc</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026CP1801197</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Dorchester</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Johnson, Tobbie</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026CP1801388</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Florence</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J G Wentworth Originations Llc</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026CP2101257</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>05/28/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Williamsburg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J G Wentworth Originations, Llc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026CP4500225</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>05/20/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>J G Wentworth Originations, Llc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026CP4601592</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J G Wentworth Originations, Llc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026CP4601826</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>05/29/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
